--- a/artfynd/A 33822-2023 artfynd.xlsx
+++ b/artfynd/A 33822-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33822-2023 artfynd.xlsx
+++ b/artfynd/A 33822-2023 artfynd.xlsx
@@ -1907,7 +1907,7 @@
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG12" t="b">
         <v>0</v>

--- a/artfynd/A 33822-2023 artfynd.xlsx
+++ b/artfynd/A 33822-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113034500</v>
+        <v>113034383</v>
       </c>
       <c r="B2" t="n">
-        <v>79184</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529742</v>
+        <v>529743</v>
       </c>
       <c r="R2" t="n">
-        <v>7030473</v>
+        <v>7030474</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,21 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -796,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113034487</v>
+        <v>113034506</v>
       </c>
       <c r="B3" t="n">
-        <v>79184</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90692</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1599</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fjällfotad musseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tricholoma olivaceotinctum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529773</v>
+        <v>529679</v>
       </c>
       <c r="R3" t="n">
-        <v>7030338</v>
+        <v>7030441</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,6 +849,11 @@
           <t>2023-09-27</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I anslutning till dike.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -882,21 +862,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -917,15 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113034435</v>
+        <v>113034464</v>
       </c>
       <c r="B4" t="n">
-        <v>56765</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,42 +893,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Mårtviksberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529682</v>
+        <v>529844</v>
       </c>
       <c r="R4" t="n">
-        <v>7030436</v>
+        <v>7030277</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,11 +955,6 @@
           <t>2023-09-27</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ganska färskt ringhack</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1016,6 +963,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1036,15 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113034408</v>
+        <v>113034488</v>
       </c>
       <c r="B5" t="n">
-        <v>79184</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,37 +1009,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mårtviksberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529673</v>
+        <v>529773</v>
       </c>
       <c r="R5" t="n">
-        <v>7030352</v>
+        <v>7030338</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,23 +1077,22 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1161,39 +1114,30 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113034442</v>
+        <v>113034468</v>
       </c>
       <c r="B6" t="n">
-        <v>79184</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87412</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>3624</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1201,10 +1145,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529650</v>
+        <v>529655</v>
       </c>
       <c r="R6" t="n">
-        <v>7030349</v>
+        <v>7030357</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1267,37 +1211,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113034383</v>
+        <v>113034453</v>
       </c>
       <c r="B7" t="n">
-        <v>90045</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1307,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529743</v>
+        <v>529688</v>
       </c>
       <c r="R7" t="n">
-        <v>7030474</v>
+        <v>7030472</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1373,37 +1312,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113034499</v>
+        <v>113034436</v>
       </c>
       <c r="B8" t="n">
-        <v>79211</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1413,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529742</v>
+        <v>529782</v>
       </c>
       <c r="R8" t="n">
-        <v>7030473</v>
+        <v>7030320</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,21 +1393,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1494,15 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113034469</v>
+        <v>113034462</v>
       </c>
       <c r="B9" t="n">
-        <v>78713</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,21 +1424,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1534,10 +1448,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529818</v>
+        <v>529844</v>
       </c>
       <c r="R9" t="n">
-        <v>7030296</v>
+        <v>7030277</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,6 +1494,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1600,37 +1529,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113034468</v>
+        <v>113034469</v>
       </c>
       <c r="B10" t="n">
-        <v>85824</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3624</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Fr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1640,10 +1564,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529654</v>
+        <v>529818</v>
       </c>
       <c r="R10" t="n">
-        <v>7030357</v>
+        <v>7030296</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,15 +1630,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113034474</v>
+        <v>113034408</v>
       </c>
       <c r="B11" t="n">
-        <v>56765</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1722,31 +1641,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1754,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529660</v>
+        <v>529674</v>
       </c>
       <c r="R11" t="n">
-        <v>7030342</v>
+        <v>7030352</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,19 +1706,30 @@
           <t>2023-09-27</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ganska färskt ringhack</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1825,15 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113034498</v>
+        <v>113034442</v>
       </c>
       <c r="B12" t="n">
-        <v>79229</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229504</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1865,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529742</v>
+        <v>529649</v>
       </c>
       <c r="R12" t="n">
-        <v>7030473</v>
+        <v>7030349</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,25 +1827,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1946,15 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113034491</v>
+        <v>113034463</v>
       </c>
       <c r="B13" t="n">
-        <v>56765</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,42 +1862,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mårtviksberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529732</v>
+        <v>529844</v>
       </c>
       <c r="R13" t="n">
-        <v>7030453</v>
+        <v>7030277</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2032,11 +1924,6 @@
           <t>2023-09-27</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2045,6 +1932,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2065,15 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113034436</v>
+        <v>113034467</v>
       </c>
       <c r="B14" t="n">
-        <v>74302</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2081,21 +1978,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2105,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529782</v>
+        <v>529655</v>
       </c>
       <c r="R14" t="n">
-        <v>7030320</v>
+        <v>7030357</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2171,15 +2068,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113034488</v>
+        <v>113034487</v>
       </c>
       <c r="B15" t="n">
-        <v>79185</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2187,21 +2079,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2292,15 +2184,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113034467</v>
+        <v>113034500</v>
       </c>
       <c r="B16" t="n">
-        <v>79184</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529654</v>
+        <v>529742</v>
       </c>
       <c r="R16" t="n">
-        <v>7030357</v>
+        <v>7030473</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2379,6 +2266,21 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
@@ -2391,6 +2293,696 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>113034499</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mårtviksberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>529742</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7030473</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>113034460</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mårtviksberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>529844</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7030277</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>113034435</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mårtviksberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>529681</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7030436</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ganska färskt ringhack</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>113034474</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mårtviksberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>529661</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7030342</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ganska färskt ringhack</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>113034491</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mårtviksberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>529732</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7030453</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>113034498</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80477</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mårtviksberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>529742</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7030473</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Borgvattnet</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>

--- a/artfynd/A 33822-2023 artfynd.xlsx
+++ b/artfynd/A 33822-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113034383</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113034506</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113034464</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113034488</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1208,6 +1233,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113034468</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1309,6 +1339,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113034453</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,6 +1445,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113034436</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1526,6 +1566,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113034462</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1625,6 +1670,11 @@
       <c r="AY10" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113034469</t>
         </is>
       </c>
     </row>
@@ -1747,6 +1797,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113034408</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1848,6 +1903,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113034442</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1964,6 +2024,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113034463</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2065,6 +2130,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113034467</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2181,6 +2251,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113034487</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2297,6 +2372,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113034500</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2413,6 +2493,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113034499</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2529,6 +2614,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113034460</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2643,6 +2733,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113034435</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2757,6 +2852,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113034474</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2871,6 +2971,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113034491</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2987,8 +3092,36 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113034498</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>